--- a/data/trans_dic/P34B02_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,89</t>
+          <t>5,73; 10,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,74</t>
+          <t>7,56; 13,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,56; 46,07</t>
+          <t>28,32; 46,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,42</t>
+          <t>3,28; 7,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,39</t>
+          <t>5,9; 11,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 29,1</t>
+          <t>17,36; 30,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,32</t>
+          <t>5,02; 8,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,49</t>
+          <t>7,64; 11,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,7; 36,62</t>
+          <t>25,24; 36,1</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,89</t>
+          <t>4,23; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 15,97</t>
+          <t>10,05; 15,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 30,17</t>
+          <t>18,86; 29,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,83</t>
+          <t>2,4; 5,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,43</t>
+          <t>3,8; 7,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 16,39</t>
+          <t>7,38; 16,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,33</t>
+          <t>3,81; 6,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,11</t>
+          <t>7,71; 11,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,64; 21,19</t>
+          <t>13,23; 21,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,34</t>
+          <t>3,88; 7,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,75</t>
+          <t>6,43; 10,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,85; 27,21</t>
+          <t>20,03; 27,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,86</t>
+          <t>2,2; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,66</t>
+          <t>5,54; 9,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,79; 19,18</t>
+          <t>13,56; 18,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,57</t>
+          <t>3,44; 5,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,55</t>
+          <t>6,45; 9,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,01</t>
+          <t>17,45; 22,17</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,82</t>
+          <t>3,32; 6,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,59</t>
+          <t>4,93; 8,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 18,92</t>
+          <t>5,84; 19,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,56</t>
+          <t>2,71; 6,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,88</t>
+          <t>2,82; 5,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,47</t>
+          <t>12,48; 17,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,96</t>
+          <t>3,44; 6,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,93</t>
+          <t>4,16; 6,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 17,17</t>
+          <t>8,92; 17,53</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,43</t>
+          <t>2,45; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,58</t>
+          <t>2,71; 6,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,94</t>
+          <t>12,85; 18,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,3</t>
+          <t>3,74; 8,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,76</t>
+          <t>2,77; 6,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 15,36</t>
+          <t>11,02; 15,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,67</t>
+          <t>3,47; 6,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,95</t>
+          <t>3,12; 6,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 16,29</t>
+          <t>12,56; 16,24</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,63</t>
+          <t>3,64; 9,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,65</t>
+          <t>2,1; 6,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,45</t>
+          <t>7,63; 13,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,6</t>
+          <t>1,37; 4,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,21</t>
+          <t>2,03; 6,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 11,16</t>
+          <t>2,79; 11,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,13</t>
+          <t>2,71; 6,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,61</t>
+          <t>2,64; 5,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,88</t>
+          <t>4,38; 10,96</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,3</t>
+          <t>0,42; 4,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,46</t>
+          <t>0,6; 3,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,8</t>
+          <t>3,39; 8,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,33</t>
+          <t>0,53; 3,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,4</t>
+          <t>1,25; 5,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,46</t>
+          <t>2,79; 5,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,9</t>
+          <t>0,68; 2,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,11</t>
+          <t>1,24; 3,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,02</t>
+          <t>3,39; 5,87</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,25</t>
+          <t>4,66; 6,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,53</t>
+          <t>6,66; 8,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,41</t>
+          <t>14,31; 20,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,53</t>
+          <t>3,19; 4,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,22</t>
+          <t>4,62; 6,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,59; 13,86</t>
+          <t>10,43; 13,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,1</t>
+          <t>4,07; 5,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,98</t>
+          <t>5,8; 7,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,31; 16,66</t>
+          <t>13,25; 16,7</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25827; 49321</t>
+          <t>25951; 49351</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31729; 57639</t>
+          <t>31698; 56628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114252; 184260</t>
+          <t>113289; 184074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13600; 31908</t>
+          <t>14127; 33081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23724; 45075</t>
+          <t>23340; 45689</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55043; 91084</t>
+          <t>54337; 93937</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44337; 73449</t>
+          <t>44336; 72570</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62219; 93648</t>
+          <t>62292; 95139</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>183279; 261093</t>
+          <t>180002; 257380</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29229; 54142</t>
+          <t>29044; 52641</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60850; 94309</t>
+          <t>59324; 92945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80695; 127096</t>
+          <t>79454; 125914</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14189; 35581</t>
+          <t>14637; 35614</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21507; 41894</t>
+          <t>21436; 42882</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38421; 83810</t>
+          <t>37743; 84251</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49642; 82014</t>
+          <t>49354; 81648</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89448; 128249</t>
+          <t>88960; 128572</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127227; 197660</t>
+          <t>123389; 199486</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26735; 50083</t>
+          <t>26448; 50638</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41632; 71956</t>
+          <t>43010; 72256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106445; 145911</t>
+          <t>107388; 147201</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15660; 34434</t>
+          <t>15593; 35089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37939; 63881</t>
+          <t>36639; 64919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74609; 103769</t>
+          <t>73345; 101353</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47210; 77518</t>
+          <t>47789; 78115</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86780; 127050</t>
+          <t>85873; 127535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>188118; 237040</t>
+          <t>187968; 238800</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20360; 41892</t>
+          <t>20385; 42740</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30032; 55521</t>
+          <t>31845; 57494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46889; 167939</t>
+          <t>51822; 172032</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17816; 40434</t>
+          <t>16682; 39388</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18400; 38161</t>
+          <t>18295; 38838</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89392; 124468</t>
+          <t>88917; 124558</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42231; 73346</t>
+          <t>42392; 74293</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55646; 89739</t>
+          <t>53893; 88540</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132075; 274692</t>
+          <t>142668; 280565</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11593; 27617</t>
+          <t>10531; 27761</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13864; 31465</t>
+          <t>12956; 31074</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72182; 105844</t>
+          <t>71773; 103833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16928; 37157</t>
+          <t>16762; 38704</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13077; 33584</t>
+          <t>13751; 33446</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61061; 83806</t>
+          <t>60142; 84097</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31664; 58487</t>
+          <t>30467; 57288</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30147; 58046</t>
+          <t>30395; 58857</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>139542; 179840</t>
+          <t>138727; 179298</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11733; 29836</t>
+          <t>11267; 29567</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7615; 22244</t>
+          <t>7019; 21531</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28896; 49520</t>
+          <t>28076; 48099</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4821; 16271</t>
+          <t>4858; 16086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7537; 23455</t>
+          <t>7662; 23257</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16793; 67870</t>
+          <t>16951; 67290</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17890; 40696</t>
+          <t>17957; 40318</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18246; 39964</t>
+          <t>18815; 40322</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42830; 106273</t>
+          <t>42800; 106996</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1141; 10737</t>
+          <t>1059; 10817</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1584; 8883</t>
+          <t>1543; 9029</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9676; 22046</t>
+          <t>9597; 22776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2115; 12942</t>
+          <t>2073; 12590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5058; 21607</t>
+          <t>5003; 20470</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12102; 23179</t>
+          <t>11860; 23524</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5209; 18530</t>
+          <t>4364; 17873</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8156; 27024</t>
+          <t>8167; 26049</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25197; 42623</t>
+          <t>24009; 41500</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>159461; 213959</t>
+          <t>159752; 213869</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>225471; 289648</t>
+          <t>226105; 291049</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>483064; 704999</t>
+          <t>494412; 704076</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>112404; 160957</t>
+          <t>113574; 163496</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>160398; 220525</t>
+          <t>163789; 217341</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>387261; 506874</t>
+          <t>381246; 510352</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>285254; 356338</t>
+          <t>284181; 358510</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>404184; 484009</t>
+          <t>402679; 485913</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>946294; 1185050</t>
+          <t>941990; 1187365</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B02_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,89</t>
+          <t>5,79; 10,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,5</t>
+          <t>7,89; 13,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,32; 46,02</t>
+          <t>30,21; 44,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,69</t>
+          <t>3,33; 7,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,54</t>
+          <t>6,01; 11,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 30,01</t>
+          <t>17,69; 28,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,22</t>
+          <t>5,09; 8,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,67</t>
+          <t>7,57; 11,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,24; 36,1</t>
+          <t>25,49; 35,34</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,67</t>
+          <t>4,18; 7,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,74</t>
+          <t>10,66; 16,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 29,89</t>
+          <t>19,63; 29,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,84</t>
+          <t>2,44; 5,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,61</t>
+          <t>3,84; 7,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 16,47</t>
+          <t>11,33; 17,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,3</t>
+          <t>3,77; 6,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,14</t>
+          <t>7,62; 11,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,23; 21,39</t>
+          <t>16,32; 22,53</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,43</t>
+          <t>3,89; 7,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,8</t>
+          <t>6,39; 10,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,03; 27,45</t>
+          <t>19,37; 26,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,95</t>
+          <t>2,2; 4,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,82</t>
+          <t>5,59; 9,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 18,74</t>
+          <t>13,37; 18,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,62</t>
+          <t>3,33; 5,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,59</t>
+          <t>6,5; 9,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,45; 22,17</t>
+          <t>17,04; 21,29</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,95</t>
+          <t>3,22; 6,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,9</t>
+          <t>4,64; 8,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 19,38</t>
+          <t>15,01; 20,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,39</t>
+          <t>2,71; 6,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,98</t>
+          <t>2,74; 5,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 17,48</t>
+          <t>13,56; 17,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,04</t>
+          <t>3,48; 6,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,84</t>
+          <t>4,27; 6,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 17,53</t>
+          <t>14,68; 18,19</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,46</t>
+          <t>2,52; 6,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,5</t>
+          <t>2,74; 6,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 18,58</t>
+          <t>13,06; 18,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,64</t>
+          <t>3,72; 8,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,73</t>
+          <t>2,75; 7,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,02; 15,41</t>
+          <t>10,88; 14,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,53</t>
+          <t>3,63; 6,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,04</t>
+          <t>3,08; 5,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 16,24</t>
+          <t>12,53; 16,2</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,54</t>
+          <t>3,64; 9,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,44</t>
+          <t>2,28; 6,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,06</t>
+          <t>8,27; 13,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,54</t>
+          <t>1,37; 4,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,16</t>
+          <t>2,01; 6,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,06</t>
+          <t>8,23; 12,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,07</t>
+          <t>2,83; 6,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,66</t>
+          <t>2,62; 5,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,96</t>
+          <t>8,93; 12,19</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,33</t>
+          <t>0,45; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,51</t>
+          <t>0,6; 3,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,05</t>
+          <t>3,43; 7,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,24</t>
+          <t>0,54; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,12</t>
+          <t>1,25; 5,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,54</t>
+          <t>2,69; 5,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,8</t>
+          <t>0,68; 2,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,96</t>
+          <t>1,28; 3,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,87</t>
+          <t>3,55; 5,93</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,24</t>
+          <t>4,63; 6,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,57</t>
+          <t>6,65; 8,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,31; 20,38</t>
+          <t>17,99; 21,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,6</t>
+          <t>3,16; 4,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,13</t>
+          <t>4,58; 6,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,96</t>
+          <t>12,61; 14,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,14</t>
+          <t>4,05; 5,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,0</t>
+          <t>5,8; 7,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,7</t>
+          <t>15,56; 17,41</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148063</t>
+          <t>150727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70350</t>
+          <t>81432</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>218413</t>
+          <t>232159</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25951; 49351</t>
+          <t>26248; 49507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31698; 56628</t>
+          <t>33089; 57101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113289; 184074</t>
+          <t>123214; 181885</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14127; 33081</t>
+          <t>14342; 31703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23340; 45689</t>
+          <t>23794; 45718</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54337; 93937</t>
+          <t>63689; 103779</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44336; 72570</t>
+          <t>44963; 73547</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62292; 95139</t>
+          <t>61709; 96032</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>180002; 257380</t>
+          <t>195709; 271378</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101161</t>
+          <t>116140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>165410</t>
+          <t>187755</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29044; 52641</t>
+          <t>28708; 54234</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59324; 92945</t>
+          <t>62932; 95399</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79454; 125914</t>
+          <t>93144; 141680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14637; 35614</t>
+          <t>14884; 36224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21436; 42882</t>
+          <t>21665; 43447</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37743; 84251</t>
+          <t>56772; 88545</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49354; 81648</t>
+          <t>48826; 81625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88960; 128572</t>
+          <t>87888; 128529</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>123389; 199486</t>
+          <t>159190; 219769</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125978</t>
+          <t>141828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87903</t>
+          <t>96298</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>213881</t>
+          <t>238126</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26448; 50638</t>
+          <t>26521; 50519</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43010; 72256</t>
+          <t>42759; 73230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107388; 147201</t>
+          <t>120025; 164786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15593; 35089</t>
+          <t>15564; 34917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36639; 64919</t>
+          <t>36982; 65799</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73345; 101353</t>
+          <t>82888; 112974</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47789; 78115</t>
+          <t>46355; 76513</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85873; 127535</t>
+          <t>86544; 128050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>187968; 238800</t>
+          <t>211282; 263850</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115544</t>
+          <t>123849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>107371</t>
+          <t>114067</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>222916</t>
+          <t>237916</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20385; 42740</t>
+          <t>19768; 42411</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31845; 57494</t>
+          <t>29988; 57816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51822; 172032</t>
+          <t>105181; 145457</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16682; 39388</t>
+          <t>16698; 39075</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18295; 38838</t>
+          <t>17774; 38795</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88917; 124558</t>
+          <t>99875; 129687</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42392; 74293</t>
+          <t>42839; 76400</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53893; 88540</t>
+          <t>55303; 87972</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142668; 280565</t>
+          <t>210944; 261407</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87024</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71847</t>
+          <t>78634</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>158871</t>
+          <t>174856</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10531; 27761</t>
+          <t>10826; 28338</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12956; 31074</t>
+          <t>13102; 30891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71773; 103833</t>
+          <t>79210; 114594</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16762; 38704</t>
+          <t>16672; 38294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13751; 33446</t>
+          <t>13685; 34981</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60142; 84097</t>
+          <t>66165; 90801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30467; 57288</t>
+          <t>31840; 60193</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30395; 58857</t>
+          <t>29993; 57909</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>138727; 179298</t>
+          <t>152185; 196785</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>45078</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>78964</t>
+          <t>88729</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11267; 29567</t>
+          <t>11277; 30166</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7019; 21531</t>
+          <t>7612; 22961</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28076; 48099</t>
+          <t>33673; 55947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4858; 16086</t>
+          <t>4863; 16137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7662; 23257</t>
+          <t>7580; 23110</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16951; 67290</t>
+          <t>36157; 55692</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17957; 40318</t>
+          <t>18762; 41452</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18815; 40322</t>
+          <t>18677; 41099</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42800; 106996</t>
+          <t>75574; 103175</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>35113</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1059; 10817</t>
+          <t>1120; 10959</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1543; 9029</t>
+          <t>1530; 9078</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9597; 22776</t>
+          <t>10630; 24765</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2073; 12590</t>
+          <t>2086; 12314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5003; 20470</t>
+          <t>4998; 20265</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11860; 23524</t>
+          <t>12474; 25273</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4364; 17873</t>
+          <t>4356; 17924</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8167; 26049</t>
+          <t>8408; 25175</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24009; 41500</t>
+          <t>27445; 45910</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630884</t>
+          <t>689134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>459998</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1090881</t>
+          <t>1194654</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>159752; 213869</t>
+          <t>158657; 210159</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>226105; 291049</t>
+          <t>225886; 290355</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>494412; 704076</t>
+          <t>634269; 742774</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>113574; 163496</t>
+          <t>112463; 159792</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>163789; 217341</t>
+          <t>162356; 218899</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>381246; 510352</t>
+          <t>470003; 546123</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>284181; 358510</t>
+          <t>282956; 358909</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>402679; 485913</t>
+          <t>402471; 487216</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>941990; 1187365</t>
+          <t>1128587; 1263093</t>
         </is>
       </c>
     </row>
